--- a/public/templates/leave-annual.xlsx
+++ b/public/templates/leave-annual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10625"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ihab1980\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA638101-39A0-4F27-924F-1E92D65FFB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7FEFD8E-82DC-2649-B38C-9F650DDE276C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7D7C3881-7350-4B3B-A3A8-77028ED7EE65}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$25</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -366,13 +363,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -432,6 +428,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,365 +839,379 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="6" max="7" width="18.28515625" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.25390625" customWidth="1"/>
+    <col min="3" max="3" width="24.078125" customWidth="1"/>
+    <col min="6" max="7" width="18.29296875" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.94921875" customWidth="1"/>
+    <col min="11" max="11" width="4.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="32" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="20" t="s">
+      <c r="H1" s="32"/>
+      <c r="I1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
-    </row>
-    <row r="2" spans="1:11" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="29" t="s">
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
+    </row>
+    <row r="2" spans="1:11" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26"/>
+      <c r="B2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="31"/>
+      <c r="E2" s="30"/>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="33"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H2" s="32"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="17" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="A6" s="7"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="18" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="24.75" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="16" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="16" t="s">
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="16" t="s">
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="16" t="s">
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="17" t="s">
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="16" t="s">
+      <c r="G13" s="14"/>
+      <c r="H13" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="9"/>
-    </row>
-    <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="16" t="s">
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A18" s="14"/>
-      <c r="B18" s="16" t="s">
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="13"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="16" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A20" s="14"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="J25" s="3" t="s">
+      <c r="J18" s="14"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="33" t="s">
         <v>19</v>
       </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="15">
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="I1:K2"/>
     <mergeCell ref="A1:A2"/>
@@ -1204,6 +1220,7 @@
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G8:I8"/>
   </mergeCells>
   <pageMargins left="0.25" right="0" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" scale="68" orientation="landscape" r:id="rId1"/>
